--- a/website/examples/example_odk_nfc_credential_verification.xlsx
+++ b/website/examples/example_odk_nfc_credential_verification.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Ra8b7948270174c59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rcca78d2f7b6e4992"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R90e2a04c0c5948ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R1104b7ce102440a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R8c10b82837a049b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R2be47fb2623e4f6c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -349,7 +349,7 @@
         <x:v>Verify a portable NFC credential</x:v>
       </x:c>
       <x:c r="D4" s="3" t="str">
-        <x:v>ResearchOS reads the card and asks for its PIN. The PIN remains inside ResearchOS and is never saved in this form.</x:v>
+        <x:v>MethodMesh reads the card and asks for its PIN. The PIN remains inside MethodMesh and is never saved in this form.</x:v>
       </x:c>
       <x:c r="E4" s="3" t="str"/>
       <x:c r="F4" s="3" t="str"/>
@@ -368,13 +368,13 @@
         <x:v>nfc_credential_verification</x:v>
       </x:c>
       <x:c r="D5" s="3" t="str">
-        <x:v>Tap the credential, then enter its PIN inside ResearchOS.</x:v>
+        <x:v>Tap the credential, then enter its PIN inside MethodMesh.</x:v>
       </x:c>
       <x:c r="E5" s="3" t="str">
         <x:v>field-list</x:v>
       </x:c>
       <x:c r="F5" s="3" t="str">
-        <x:v>com.example.researchos.EXECUTE_METHOD(method_id='nfc_credential_verification',return_mode='flat')</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='nfc_credential_verification',return_mode='flat')</x:v>
       </x:c>
       <x:c r="G5" s="3" t="str"/>
       <x:c r="H5" s="3" t="str"/>
@@ -385,10 +385,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B6" s="3" t="str">
-        <x:v>researchos_execution_id</x:v>
+        <x:v>methodmesh_execution_id</x:v>
       </x:c>
       <x:c r="C6" s="3" t="str">
-        <x:v>ResearchOS execution ID</x:v>
+        <x:v>MethodMesh execution ID</x:v>
       </x:c>
       <x:c r="D6" s="3" t="str"/>
       <x:c r="E6" s="3" t="str"/>
@@ -402,10 +402,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B7" s="3" t="str">
-        <x:v>researchos_status</x:v>
+        <x:v>methodmesh_status</x:v>
       </x:c>
       <x:c r="C7" s="3" t="str">
-        <x:v>ResearchOS status</x:v>
+        <x:v>MethodMesh status</x:v>
       </x:c>
       <x:c r="D7" s="3" t="str"/>
       <x:c r="E7" s="3" t="str"/>
